--- a/public/assets/files/Tableau_competences_BTS.xlsx
+++ b/public/assets/files/Tableau_competences_BTS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BTS-SIO-ORT\2em-annee\stage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avita\Documents\Portfolio_Avital_Sika\Portfolio_new\public\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{29F3B12A-1BA1-4113-85B4-78447AB30682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FEE42EC8-30FC-46E1-A3EC-6016371AA123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="37">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -66,9 +66,6 @@
   </si>
   <si>
     <t>▢ SLAM</t>
-  </si>
-  <si>
-    <t>Adresse URL du portfolio :</t>
   </si>
   <si>
     <t>Compétences mises en œuvre
@@ -162,6 +159,15 @@
   </si>
   <si>
     <t>Du 05/01/2025 au 06/02/2025</t>
+  </si>
+  <si>
+    <t>Adresse URL du portfolio :  https://avitalsika.vercel.app/</t>
+  </si>
+  <si>
+    <t>De 02/2026 à 03/2026</t>
+  </si>
+  <si>
+    <t>X</t>
   </si>
 </sst>
 </file>
@@ -243,12 +249,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="16"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -267,22 +267,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="28"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="46">
+  <borders count="50">
     <border>
       <left/>
       <right/>
@@ -621,21 +621,6 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
       <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
@@ -643,69 +628,304 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color theme="2" tint="-0.749992370372631"/>
       </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
       </left>
       <right style="thin">
         <color theme="2" tint="-0.749992370372631"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
       </left>
       <right style="thin">
         <color theme="2" tint="-0.749992370372631"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top/>
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
       </left>
       <right style="thin">
         <color rgb="FF000000"/>
@@ -721,150 +941,10 @@
         <color rgb="FF000000"/>
       </left>
       <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
@@ -876,7 +956,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -932,6 +1012,42 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -956,47 +1072,81 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1004,106 +1154,37 @@
     <xf numFmtId="14" fontId="11" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1493,56 +1574,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19" t="s">
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="20"/>
+      <c r="H1" s="32"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="31"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="24"/>
     </row>
     <row r="3" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="24" t="s">
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="25"/>
-      <c r="H3" s="26"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="38"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
       <c r="F4" s="6" t="s">
         <v>6</v>
       </c>
@@ -1554,63 +1635,63 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="28"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="30"/>
+    </row>
+    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="38"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="40"/>
-    </row>
-    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="27" t="s">
+      <c r="B6" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="C6" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="D6" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="E6" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="F6" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="G6" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="H6" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="14" t="s">
+    </row>
+    <row r="7" spans="1:43" s="2" customFormat="1" ht="324.89999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="21"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="9" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:43" s="2" customFormat="1" ht="324.89999999999998" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="28"/>
-      <c r="B7" s="36"/>
-      <c r="C7" s="9" t="s">
+      <c r="D7" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="E7" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="F7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="G7" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="H7" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>23</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -1648,17 +1729,17 @@
       <c r="AP7"/>
       <c r="AQ7"/>
     </row>
-    <row r="8" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A8" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="34"/>
+    <row r="8" spans="1:43" s="2" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="47"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="47"/>
+      <c r="E8" s="47"/>
+      <c r="F8" s="47"/>
+      <c r="G8" s="47"/>
+      <c r="H8" s="48"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1696,19 +1777,31 @@
       <c r="AQ8"/>
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="41" t="s">
+      <c r="A9" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="42" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="43"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="45"/>
-      <c r="I9"/>
+      <c r="C9" s="67" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="67" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="67" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="67" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="67" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="68" t="s">
+        <v>36</v>
+      </c>
+      <c r="I9" s="41"/>
       <c r="J9"/>
       <c r="K9"/>
       <c r="L9"/>
@@ -1745,19 +1838,29 @@
       <c r="AQ9"/>
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="46" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="47" t="s">
+      <c r="A10" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="48"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="48"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="48"/>
-      <c r="H10" s="50"/>
-      <c r="I10"/>
+      <c r="B10" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="40"/>
+      <c r="F10" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10" s="70" t="s">
+        <v>36</v>
+      </c>
+      <c r="I10" s="41"/>
       <c r="J10"/>
       <c r="K10"/>
       <c r="L10"/>
@@ -1794,16 +1897,26 @@
       <c r="AQ10"/>
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="51"/>
-      <c r="C11" s="48"/>
-      <c r="D11" s="48"/>
-      <c r="E11" s="48"/>
-      <c r="F11" s="48"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="50"/>
+      <c r="A11" s="69" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="40"/>
+      <c r="E11" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="40"/>
+      <c r="G11" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="H11" s="70" t="s">
+        <v>36</v>
+      </c>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
@@ -1841,14 +1954,14 @@
       <c r="AQ11"/>
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="52"/>
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
-      <c r="D12" s="53"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="53"/>
-      <c r="H12" s="54"/>
+      <c r="A12" s="71"/>
+      <c r="B12" s="45"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="72"/>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
@@ -1886,14 +1999,14 @@
       <c r="AQ12"/>
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="52"/>
-      <c r="B13" s="53"/>
-      <c r="C13" s="53"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="54"/>
+      <c r="A13" s="73"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="74"/>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
@@ -1930,15 +2043,15 @@
       <c r="AP13"/>
       <c r="AQ13"/>
     </row>
-    <row r="14" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="55"/>
-      <c r="B14" s="56"/>
-      <c r="C14" s="56"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="56"/>
-      <c r="F14" s="56"/>
-      <c r="G14" s="56"/>
-      <c r="H14" s="57"/>
+    <row r="14" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="75"/>
+      <c r="B14" s="76"/>
+      <c r="C14" s="76"/>
+      <c r="D14" s="76"/>
+      <c r="E14" s="76"/>
+      <c r="F14" s="76"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="77"/>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
@@ -1975,17 +2088,17 @@
       <c r="AP14"/>
       <c r="AQ14"/>
     </row>
-    <row r="15" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="58" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="59"/>
-      <c r="C15" s="59"/>
-      <c r="D15" s="59"/>
-      <c r="E15" s="59"/>
-      <c r="F15" s="59"/>
-      <c r="G15" s="59"/>
-      <c r="H15" s="60"/>
+    <row r="15" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="57" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="58"/>
+      <c r="C15" s="58"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="59"/>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
@@ -2022,19 +2135,27 @@
       <c r="AP15"/>
       <c r="AQ15"/>
     </row>
-    <row r="16" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="61" t="s">
+    <row r="16" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="60" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="61" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="62" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" s="63"/>
+      <c r="C16" s="62" t="s">
+        <v>36</v>
+      </c>
       <c r="D16" s="63"/>
       <c r="E16" s="63"/>
-      <c r="F16" s="63"/>
-      <c r="G16" s="63"/>
-      <c r="H16" s="64"/>
+      <c r="F16" s="62" t="s">
+        <v>36</v>
+      </c>
+      <c r="G16" s="62" t="s">
+        <v>36</v>
+      </c>
+      <c r="H16" s="64" t="s">
+        <v>36</v>
+      </c>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
@@ -2071,17 +2192,17 @@
       <c r="AP16"/>
       <c r="AQ16"/>
     </row>
-    <row r="17" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="65" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="66"/>
-      <c r="C17" s="66"/>
-      <c r="D17" s="66"/>
-      <c r="E17" s="66"/>
-      <c r="F17" s="66"/>
-      <c r="G17" s="66"/>
-      <c r="H17" s="67"/>
+    <row r="17" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="57" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="58"/>
+      <c r="C17" s="58"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="58"/>
+      <c r="G17" s="58"/>
+      <c r="H17" s="59"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
@@ -2119,18 +2240,30 @@
       <c r="AQ17"/>
     </row>
     <row r="18" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="68" t="s">
+      <c r="A18" s="49" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="69" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" s="70"/>
-      <c r="D18" s="70"/>
-      <c r="E18" s="70"/>
-      <c r="F18" s="70"/>
-      <c r="G18" s="70"/>
-      <c r="H18" s="71"/>
+      <c r="C18" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="H18" s="52" t="s">
+        <v>36</v>
+      </c>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -2167,15 +2300,15 @@
       <c r="AP18"/>
       <c r="AQ18"/>
     </row>
-    <row r="19" spans="1:43" s="2" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="72"/>
-      <c r="B19" s="73"/>
-      <c r="C19" s="74"/>
-      <c r="D19" s="74"/>
-      <c r="E19" s="74"/>
-      <c r="F19" s="74"/>
-      <c r="G19" s="74"/>
-      <c r="H19" s="75"/>
+    <row r="19" spans="1:43" s="2" customFormat="1" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="53"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="55"/>
+      <c r="D19" s="55"/>
+      <c r="E19" s="55"/>
+      <c r="F19" s="55"/>
+      <c r="G19" s="55"/>
+      <c r="H19" s="56"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -2213,14 +2346,14 @@
       <c r="AQ19"/>
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="76"/>
-      <c r="B20" s="76"/>
-      <c r="C20" s="76"/>
-      <c r="D20" s="76"/>
-      <c r="E20" s="76"/>
-      <c r="F20" s="76"/>
-      <c r="G20" s="76"/>
-      <c r="H20" s="76"/>
+      <c r="A20" s="19"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -2980,6 +3113,11 @@
     <row r="81" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2987,17 +3125,12 @@
     <mergeCell ref="A17:H17"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="48" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="48" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/public/assets/files/Tableau_competences_BTS.xlsx
+++ b/public/assets/files/Tableau_competences_BTS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avita\Documents\Portfolio_Avital_Sika\Portfolio_new\public\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FEE42EC8-30FC-46E1-A3EC-6016371AA123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{796D145E-479C-4AFC-AB20-67F4ED462824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,9 +53,6 @@
     <t>NOM et prénom : SIKA Avital</t>
   </si>
   <si>
-    <t xml:space="preserve">N° candidat : </t>
-  </si>
-  <si>
     <t>Centre de formation :  ORT DANIEL MAYER</t>
   </si>
   <si>
@@ -168,6 +165,9 @@
   </si>
   <si>
     <t>X</t>
+  </si>
+  <si>
+    <t>N° candidat : 02148588400</t>
   </si>
 </sst>
 </file>
@@ -956,7 +956,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1015,6 +1015,126 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1030,6 +1150,24 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -1047,145 +1185,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1574,124 +1573,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31" t="s">
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="32"/>
+      <c r="H1" s="53"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="24"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="64"/>
     </row>
     <row r="3" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="36" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="37"/>
-      <c r="H3" s="38"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="57" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="58"/>
+      <c r="H3" s="59"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="57" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="6" t="s">
+      <c r="G4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="H4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="8" t="s">
+    </row>
+    <row r="5" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="73" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="74"/>
+      <c r="C5" s="75"/>
+      <c r="D5" s="75"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="76"/>
+    </row>
+    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="60" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="28"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="30"/>
-    </row>
-    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="20" t="s">
+      <c r="B6" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="C6" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="D6" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="E6" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="F6" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="G6" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="H6" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="14" t="s">
+    </row>
+    <row r="7" spans="1:43" s="2" customFormat="1" ht="324.89999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="61"/>
+      <c r="B7" s="72"/>
+      <c r="C7" s="9" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:43" s="2" customFormat="1" ht="324.89999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="21"/>
-      <c r="B7" s="26"/>
-      <c r="C7" s="9" t="s">
+      <c r="D7" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="E7" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="F7" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="G7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="H7" s="11" t="s">
         <v>21</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>22</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -1730,16 +1729,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47"/>
-      <c r="H8" s="48"/>
+      <c r="A8" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="66"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="67"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1777,31 +1776,31 @@
       <c r="AQ8"/>
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="65" t="s">
+      <c r="A9" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="66" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="67" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="67" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="67" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" s="67" t="s">
-        <v>36</v>
-      </c>
-      <c r="G9" s="67" t="s">
-        <v>36</v>
-      </c>
-      <c r="H9" s="68" t="s">
-        <v>36</v>
-      </c>
-      <c r="I9" s="41"/>
+      <c r="C9" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
       <c r="L9"/>
@@ -1838,29 +1837,29 @@
       <c r="AQ9"/>
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="69" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="43" t="s">
+      <c r="A10" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" s="40"/>
-      <c r="F10" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="H10" s="70" t="s">
-        <v>36</v>
-      </c>
-      <c r="I10" s="41"/>
+      <c r="B10" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="21"/>
+      <c r="F10" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10"/>
       <c r="J10"/>
       <c r="K10"/>
       <c r="L10"/>
@@ -1897,25 +1896,25 @@
       <c r="AQ10"/>
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="44" t="s">
+      <c r="A11" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" s="40"/>
-      <c r="E11" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" s="40"/>
-      <c r="G11" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="H11" s="70" t="s">
-        <v>36</v>
+      <c r="D11" s="21"/>
+      <c r="E11" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="21"/>
+      <c r="G11" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" s="44" t="s">
+        <v>35</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -1954,14 +1953,14 @@
       <c r="AQ11"/>
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="71"/>
-      <c r="B12" s="45"/>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="72"/>
+      <c r="A12" s="45"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="46"/>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
@@ -1999,14 +1998,14 @@
       <c r="AQ12"/>
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="73"/>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="74"/>
+      <c r="A13" s="47"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="48"/>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
@@ -2044,14 +2043,14 @@
       <c r="AQ13"/>
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="75"/>
-      <c r="B14" s="76"/>
-      <c r="C14" s="76"/>
-      <c r="D14" s="76"/>
-      <c r="E14" s="76"/>
-      <c r="F14" s="76"/>
-      <c r="G14" s="76"/>
-      <c r="H14" s="77"/>
+      <c r="A14" s="49"/>
+      <c r="B14" s="50"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="50"/>
+      <c r="H14" s="51"/>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
@@ -2089,16 +2088,16 @@
       <c r="AQ14"/>
     </row>
     <row r="15" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="57" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="58"/>
-      <c r="C15" s="58"/>
-      <c r="D15" s="58"/>
-      <c r="E15" s="58"/>
-      <c r="F15" s="58"/>
-      <c r="G15" s="58"/>
-      <c r="H15" s="59"/>
+      <c r="A15" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="69"/>
+      <c r="C15" s="69"/>
+      <c r="D15" s="69"/>
+      <c r="E15" s="69"/>
+      <c r="F15" s="69"/>
+      <c r="G15" s="69"/>
+      <c r="H15" s="70"/>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
@@ -2136,25 +2135,25 @@
       <c r="AQ15"/>
     </row>
     <row r="16" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="61" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="62" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="63"/>
-      <c r="E16" s="63"/>
-      <c r="F16" s="62" t="s">
-        <v>36</v>
-      </c>
-      <c r="G16" s="62" t="s">
-        <v>36</v>
-      </c>
-      <c r="H16" s="64" t="s">
-        <v>36</v>
+      <c r="C16" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="37"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" s="38" t="s">
+        <v>35</v>
       </c>
       <c r="I16"/>
       <c r="J16"/>
@@ -2193,16 +2192,16 @@
       <c r="AQ16"/>
     </row>
     <row r="17" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="57" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="58"/>
-      <c r="C17" s="58"/>
-      <c r="D17" s="58"/>
-      <c r="E17" s="58"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="58"/>
-      <c r="H17" s="59"/>
+      <c r="A17" s="68" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="69"/>
+      <c r="C17" s="69"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="69"/>
+      <c r="F17" s="69"/>
+      <c r="G17" s="69"/>
+      <c r="H17" s="70"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
@@ -2240,29 +2239,29 @@
       <c r="AQ17"/>
     </row>
     <row r="18" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="49" t="s">
+      <c r="A18" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="F18" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="G18" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="H18" s="52" t="s">
-        <v>36</v>
+      <c r="C18" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="F18" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="G18" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="H18" s="29" t="s">
+        <v>35</v>
       </c>
       <c r="I18"/>
       <c r="J18"/>
@@ -2301,14 +2300,14 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="53"/>
-      <c r="B19" s="54"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="55"/>
-      <c r="H19" s="56"/>
+      <c r="A19" s="30"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="33"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -3113,11 +3112,6 @@
     <row r="81" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -3125,6 +3119,11 @@
     <mergeCell ref="A17:H17"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/public/assets/files/Tableau_competences_BTS.xlsx
+++ b/public/assets/files/Tableau_competences_BTS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avita\Documents\Portfolio_Avital_Sika\Portfolio_new\public\assets\files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avita\Documents\Portfolio_Avital_Sika\public\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{796D145E-479C-4AFC-AB20-67F4ED462824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A905A04-3464-4C9E-9A29-F9E81481ED54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="39">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -158,9 +158,6 @@
     <t>Du 05/01/2025 au 06/02/2025</t>
   </si>
   <si>
-    <t>Adresse URL du portfolio :  https://avitalsika.vercel.app/</t>
-  </si>
-  <si>
     <t>De 02/2026 à 03/2026</t>
   </si>
   <si>
@@ -168,6 +165,15 @@
   </si>
   <si>
     <t>N° candidat : 02148588400</t>
+  </si>
+  <si>
+    <t>TP8 JAVA</t>
+  </si>
+  <si>
+    <t>Le 31/03/2025</t>
+  </si>
+  <si>
+    <t>Adresse URL du portfolio :  https://avitalsika.vercel.app</t>
   </si>
 </sst>
 </file>
@@ -282,7 +288,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="50">
+  <borders count="52">
     <border>
       <left/>
       <right/>
@@ -453,51 +459,6 @@
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
       <right/>
       <top style="medium">
         <color rgb="FF000000"/>
@@ -553,6 +514,355 @@
         <color theme="2" tint="-0.749992370372631"/>
       </diagonal>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
     <border diagonalDown="1">
       <left style="medium">
         <color rgb="FF000000"/>
@@ -563,43 +873,30 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
+      <bottom/>
       <diagonal style="thin">
         <color theme="2" tint="-0.749992370372631"/>
       </diagonal>
     </border>
     <border>
       <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
       <right style="thin">
         <color theme="2" tint="-0.749992370372631"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -607,208 +904,34 @@
       <left style="thin">
         <color theme="2" tint="-0.749992370372631"/>
       </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
       <right style="thin">
         <color theme="2" tint="-0.749992370372631"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color theme="2" tint="-0.749992370372631"/>
       </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
+        <color indexed="64"/>
       </right>
       <top style="medium">
         <color indexed="64"/>
@@ -820,10 +943,10 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </right>
       <top style="medium">
         <color indexed="64"/>
@@ -835,7 +958,7 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
       <right style="medium">
         <color indexed="64"/>
@@ -845,109 +968,6 @@
       </top>
       <bottom style="medium">
         <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -956,7 +976,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -973,31 +993,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1015,176 +1026,182 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1573,56 +1590,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="53"/>
+      <c r="H1" s="55"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="63"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="64"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="45"/>
     </row>
     <row r="3" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="55" t="s">
+      <c r="A3" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="57" t="s">
-        <v>36</v>
-      </c>
-      <c r="G3" s="58"/>
-      <c r="H3" s="59"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="59" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="60"/>
+      <c r="H3" s="61"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="57" t="s">
+      <c r="A4" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="58"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
       <c r="F4" s="6" t="s">
         <v>5</v>
       </c>
@@ -1634,62 +1651,62 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="73" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="74"/>
-      <c r="C5" s="75"/>
-      <c r="D5" s="75"/>
-      <c r="E5" s="75"/>
-      <c r="F5" s="75"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="76"/>
-    </row>
-    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="60" t="s">
+      <c r="A5" s="50" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="51"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="53"/>
+    </row>
+    <row r="6" spans="1:43" ht="90" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="71" t="s">
+      <c r="B6" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="324.89999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="61"/>
-      <c r="B7" s="72"/>
-      <c r="C7" s="9" t="s">
+      <c r="A7" s="66"/>
+      <c r="B7" s="67"/>
+      <c r="C7" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="70" t="s">
         <v>21</v>
       </c>
       <c r="I7"/>
@@ -1729,16 +1746,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="65" t="s">
+      <c r="A8" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="66"/>
-      <c r="C8" s="66"/>
-      <c r="D8" s="66"/>
-      <c r="E8" s="66"/>
-      <c r="F8" s="66"/>
-      <c r="G8" s="66"/>
-      <c r="H8" s="67"/>
+      <c r="B8" s="72"/>
+      <c r="C8" s="72"/>
+      <c r="D8" s="72"/>
+      <c r="E8" s="72"/>
+      <c r="F8" s="72"/>
+      <c r="G8" s="72"/>
+      <c r="H8" s="73"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1776,30 +1793,24 @@
       <c r="AQ8"/>
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="40" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="H9" s="42" t="s">
-        <v>35</v>
-      </c>
+      <c r="A9" s="62" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="63" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="64" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="64" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="74"/>
+      <c r="F9" s="74"/>
+      <c r="G9" s="64" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9" s="75"/>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
@@ -1837,27 +1848,29 @@
       <c r="AQ9"/>
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="23" t="s">
+      <c r="A10" s="62" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" s="21"/>
-      <c r="F10" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="H10" s="44" t="s">
-        <v>35</v>
+      <c r="C10" s="64" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="64" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="64" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" s="64" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="64" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10" s="65" t="s">
+        <v>34</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -1896,25 +1909,27 @@
       <c r="AQ10"/>
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="24" t="s">
+      <c r="A11" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="21"/>
-      <c r="E11" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" s="21"/>
-      <c r="G11" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="H11" s="44" t="s">
-        <v>35</v>
+      <c r="D11" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="18"/>
+      <c r="F11" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="H11" s="36" t="s">
+        <v>34</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -1953,14 +1968,26 @@
       <c r="AQ11"/>
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="45"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="46"/>
+      <c r="A12" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="18"/>
+      <c r="E12" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="18"/>
+      <c r="G12" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="H12" s="36" t="s">
+        <v>34</v>
+      </c>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
@@ -1998,14 +2025,14 @@
       <c r="AQ12"/>
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="47"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="48"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="38"/>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
@@ -2043,14 +2070,14 @@
       <c r="AQ13"/>
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="49"/>
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="50"/>
-      <c r="H14" s="51"/>
+      <c r="A14" s="39"/>
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="41"/>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
@@ -2088,16 +2115,16 @@
       <c r="AQ14"/>
     </row>
     <row r="15" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="68" t="s">
+      <c r="A15" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="69"/>
-      <c r="C15" s="69"/>
-      <c r="D15" s="69"/>
-      <c r="E15" s="69"/>
-      <c r="F15" s="69"/>
-      <c r="G15" s="69"/>
-      <c r="H15" s="70"/>
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="48"/>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
@@ -2135,25 +2162,25 @@
       <c r="AQ15"/>
     </row>
     <row r="16" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="34" t="s">
+      <c r="A16" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="35" t="s">
+      <c r="B16" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="G16" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="H16" s="38" t="s">
-        <v>35</v>
+      <c r="C16" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="G16" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="H16" s="34" t="s">
+        <v>34</v>
       </c>
       <c r="I16"/>
       <c r="J16"/>
@@ -2192,16 +2219,16 @@
       <c r="AQ16"/>
     </row>
     <row r="17" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="68" t="s">
+      <c r="A17" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="69"/>
-      <c r="C17" s="69"/>
-      <c r="D17" s="69"/>
-      <c r="E17" s="69"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="69"/>
-      <c r="H17" s="70"/>
+      <c r="B17" s="47"/>
+      <c r="C17" s="47"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="47"/>
+      <c r="H17" s="48"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
@@ -2239,29 +2266,29 @@
       <c r="AQ17"/>
     </row>
     <row r="18" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="27" t="s">
+      <c r="B18" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="E18" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="F18" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="G18" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="H18" s="29" t="s">
-        <v>35</v>
+      <c r="C18" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="G18" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="H18" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="I18"/>
       <c r="J18"/>
@@ -2300,14 +2327,14 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="30"/>
-      <c r="B19" s="31"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="33"/>
+      <c r="A19" s="26"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="29"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -2345,14 +2372,14 @@
       <c r="AQ19"/>
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="19"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
+      <c r="A20" s="16"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -2390,14 +2417,14 @@
       <c r="AQ20"/>
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
+      <c r="A21" s="15"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
       <c r="I21"/>
       <c r="J21"/>
       <c r="K21"/>
@@ -2435,14 +2462,14 @@
       <c r="AQ21"/>
     </row>
     <row r="22" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
+      <c r="A22" s="15"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22"/>
@@ -2480,14 +2507,14 @@
       <c r="AQ22"/>
     </row>
     <row r="23" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
+      <c r="A23" s="15"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
       <c r="I23"/>
       <c r="J23"/>
       <c r="K23"/>
@@ -2525,14 +2552,14 @@
       <c r="AQ23"/>
     </row>
     <row r="24" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="15"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
+      <c r="A24" s="12"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
@@ -2570,14 +2597,14 @@
       <c r="AQ24"/>
     </row>
     <row r="25" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="15"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
+      <c r="A25" s="12"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
       <c r="I25"/>
       <c r="J25"/>
       <c r="K25"/>
@@ -2615,14 +2642,14 @@
       <c r="AQ25"/>
     </row>
     <row r="26" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="15"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
+      <c r="A26" s="12"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2660,14 +2687,14 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="18"/>
+      <c r="A27" s="15"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2705,14 +2732,14 @@
       <c r="AQ27"/>
     </row>
     <row r="28" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18"/>
+      <c r="A28" s="15"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
       <c r="I28"/>
       <c r="J28"/>
       <c r="K28"/>
@@ -2750,14 +2777,14 @@
       <c r="AQ28"/>
     </row>
     <row r="29" spans="1:43" s="2" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="18"/>
+      <c r="A29" s="15"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
       <c r="I29"/>
       <c r="J29"/>
       <c r="K29"/>
@@ -2795,14 +2822,14 @@
       <c r="AQ29"/>
     </row>
     <row r="30" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="15"/>
-      <c r="B30" s="16"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
+      <c r="A30" s="12"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
       <c r="I30"/>
       <c r="J30"/>
       <c r="K30"/>
@@ -2840,14 +2867,14 @@
       <c r="AQ30"/>
     </row>
     <row r="31" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="15"/>
-      <c r="B31" s="16"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="17"/>
+      <c r="A31" s="12"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
       <c r="I31"/>
       <c r="J31"/>
       <c r="K31"/>
@@ -2885,14 +2912,14 @@
       <c r="AQ31"/>
     </row>
     <row r="32" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="15"/>
-      <c r="B32" s="16"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="17"/>
+      <c r="A32" s="12"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
       <c r="I32"/>
       <c r="J32"/>
       <c r="K32"/>
@@ -2930,14 +2957,14 @@
       <c r="AQ32"/>
     </row>
     <row r="33" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="15"/>
-      <c r="B33" s="16"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="17"/>
+      <c r="A33" s="12"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
       <c r="I33"/>
       <c r="J33"/>
       <c r="K33"/>
@@ -2975,14 +3002,14 @@
       <c r="AQ33"/>
     </row>
     <row r="34" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="15"/>
-      <c r="B34" s="16"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="17"/>
+      <c r="A34" s="12"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
       <c r="I34"/>
       <c r="J34"/>
       <c r="K34"/>
@@ -3112,6 +3139,11 @@
     <row r="81" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -3119,11 +3151,6 @@
     <mergeCell ref="A17:H17"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
